--- a/Historical Stats - Money League.xlsx
+++ b/Historical Stats - Money League.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Owner\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Owner\Documents\Fantasy Sports\Erik Money League\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9EFD33D-77C4-45E7-A897-D3A07ABE0B3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA5638E9-CEFC-494A-94B5-6DA784F5C448}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00571521-F8B7-4EE5-BF3F-816C35BB5F68}"/>
+    <workbookView xWindow="9276" yWindow="0" windowWidth="13860" windowHeight="12336" xr2:uid="{00571521-F8B7-4EE5-BF3F-816C35BB5F68}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="37">
   <si>
     <t>Year</t>
   </si>
@@ -490,7 +490,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91C732AA-F07A-4951-BC9E-EBED592A7799}">
-  <dimension ref="A1:J149"/>
+  <dimension ref="A1:J161"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="7" width="13.77734375" style="1" customWidth="1"/>
@@ -2704,7 +2704,7 @@
         <v>0</v>
       </c>
       <c r="J67" s="1">
-        <f t="shared" ref="J67:J149" si="1">IF(C67=1,1,0)</f>
+        <f t="shared" ref="J67:J161" si="1">IF(C67=1,1,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -5410,6 +5410,402 @@
         <v>0</v>
       </c>
       <c r="J149" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A150" s="1">
+        <v>2024</v>
+      </c>
+      <c r="B150" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C150" s="1">
+        <v>1</v>
+      </c>
+      <c r="D150" s="1">
+        <v>7</v>
+      </c>
+      <c r="E150" s="1">
+        <v>1708.76</v>
+      </c>
+      <c r="F150" s="1">
+        <v>1885.56</v>
+      </c>
+      <c r="G150" s="1">
+        <v>1</v>
+      </c>
+      <c r="H150" s="1">
+        <v>5</v>
+      </c>
+      <c r="I150" s="1">
+        <v>0</v>
+      </c>
+      <c r="J150" s="1">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="151" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A151" s="1">
+        <v>2024</v>
+      </c>
+      <c r="B151" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C151" s="1">
+        <v>2</v>
+      </c>
+      <c r="D151" s="1">
+        <v>8</v>
+      </c>
+      <c r="E151" s="1">
+        <v>1905.44</v>
+      </c>
+      <c r="F151" s="1">
+        <v>1850.04</v>
+      </c>
+      <c r="G151" s="1">
+        <v>1</v>
+      </c>
+      <c r="H151" s="1">
+        <v>12</v>
+      </c>
+      <c r="I151" s="1">
+        <v>0</v>
+      </c>
+      <c r="J151" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A152" s="1">
+        <v>2024</v>
+      </c>
+      <c r="B152" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C152" s="1">
+        <v>3</v>
+      </c>
+      <c r="D152" s="1">
+        <v>9</v>
+      </c>
+      <c r="E152" s="1">
+        <v>2069.86</v>
+      </c>
+      <c r="F152" s="1">
+        <v>1887.58</v>
+      </c>
+      <c r="G152" s="1">
+        <v>1</v>
+      </c>
+      <c r="H152" s="1">
+        <v>8</v>
+      </c>
+      <c r="I152" s="1">
+        <v>1</v>
+      </c>
+      <c r="J152" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A153" s="1">
+        <v>2024</v>
+      </c>
+      <c r="B153" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C153" s="1">
+        <v>4</v>
+      </c>
+      <c r="D153" s="1">
+        <v>12</v>
+      </c>
+      <c r="E153" s="1">
+        <v>1938.5</v>
+      </c>
+      <c r="F153" s="1">
+        <v>1754.56</v>
+      </c>
+      <c r="G153" s="1">
+        <v>1</v>
+      </c>
+      <c r="H153" s="1">
+        <v>9</v>
+      </c>
+      <c r="I153" s="1">
+        <v>1</v>
+      </c>
+      <c r="J153" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A154" s="1">
+        <v>2024</v>
+      </c>
+      <c r="B154" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C154" s="1">
+        <v>5</v>
+      </c>
+      <c r="D154" s="1">
+        <v>9</v>
+      </c>
+      <c r="E154" s="1">
+        <v>1868.2</v>
+      </c>
+      <c r="F154" s="1">
+        <v>1724.08</v>
+      </c>
+      <c r="G154" s="1">
+        <v>1</v>
+      </c>
+      <c r="H154" s="1">
+        <v>2</v>
+      </c>
+      <c r="I154" s="1">
+        <v>0</v>
+      </c>
+      <c r="J154" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A155" s="1">
+        <v>2024</v>
+      </c>
+      <c r="B155" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C155" s="1">
+        <v>6</v>
+      </c>
+      <c r="D155" s="1">
+        <v>8</v>
+      </c>
+      <c r="E155" s="1">
+        <v>2029.16</v>
+      </c>
+      <c r="F155" s="1">
+        <v>1760.26</v>
+      </c>
+      <c r="G155" s="1">
+        <v>1</v>
+      </c>
+      <c r="H155" s="1">
+        <v>7</v>
+      </c>
+      <c r="I155" s="1">
+        <v>0</v>
+      </c>
+      <c r="J155" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A156" s="1">
+        <v>2024</v>
+      </c>
+      <c r="B156" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C156" s="1">
+        <v>7</v>
+      </c>
+      <c r="D156" s="1">
+        <v>6</v>
+      </c>
+      <c r="E156" s="1">
+        <v>1938.58</v>
+      </c>
+      <c r="F156" s="1">
+        <v>1898.56</v>
+      </c>
+      <c r="G156" s="1">
+        <v>0</v>
+      </c>
+      <c r="H156" s="1">
+        <v>3</v>
+      </c>
+      <c r="I156" s="1">
+        <v>0</v>
+      </c>
+      <c r="J156" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A157" s="1">
+        <v>2024</v>
+      </c>
+      <c r="B157" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C157" s="1">
+        <v>8</v>
+      </c>
+      <c r="D157" s="1">
+        <v>6</v>
+      </c>
+      <c r="E157" s="1">
+        <v>1848.6</v>
+      </c>
+      <c r="F157" s="1">
+        <v>1947.88</v>
+      </c>
+      <c r="G157" s="1">
+        <v>0</v>
+      </c>
+      <c r="H157" s="1">
+        <v>4</v>
+      </c>
+      <c r="I157" s="1">
+        <v>0</v>
+      </c>
+      <c r="J157" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A158" s="1">
+        <v>2024</v>
+      </c>
+      <c r="B158" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C158" s="1">
+        <v>9</v>
+      </c>
+      <c r="D158" s="1">
+        <v>4</v>
+      </c>
+      <c r="E158" s="1">
+        <v>1877.88</v>
+      </c>
+      <c r="F158" s="1">
+        <v>2015.6</v>
+      </c>
+      <c r="G158" s="1">
+        <v>0</v>
+      </c>
+      <c r="H158" s="1">
+        <v>10</v>
+      </c>
+      <c r="I158" s="1">
+        <v>0</v>
+      </c>
+      <c r="J158" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A159" s="1">
+        <v>2024</v>
+      </c>
+      <c r="B159" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C159" s="1">
+        <v>10</v>
+      </c>
+      <c r="D159" s="1">
+        <v>6</v>
+      </c>
+      <c r="E159" s="1">
+        <v>1690.84</v>
+      </c>
+      <c r="F159" s="1">
+        <v>1784</v>
+      </c>
+      <c r="G159" s="1">
+        <v>0</v>
+      </c>
+      <c r="H159" s="1">
+        <v>1</v>
+      </c>
+      <c r="I159" s="1">
+        <v>0</v>
+      </c>
+      <c r="J159" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A160" s="1">
+        <v>2024</v>
+      </c>
+      <c r="B160" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C160" s="1">
+        <v>11</v>
+      </c>
+      <c r="D160" s="1">
+        <v>4</v>
+      </c>
+      <c r="E160" s="1">
+        <v>1702.36</v>
+      </c>
+      <c r="F160" s="1">
+        <v>1944.46</v>
+      </c>
+      <c r="G160" s="1">
+        <v>0</v>
+      </c>
+      <c r="H160" s="1">
+        <v>11</v>
+      </c>
+      <c r="I160" s="1">
+        <v>0</v>
+      </c>
+      <c r="J160" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A161" s="1">
+        <v>2024</v>
+      </c>
+      <c r="B161" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C161" s="1">
+        <v>12</v>
+      </c>
+      <c r="D161" s="1">
+        <v>5</v>
+      </c>
+      <c r="E161" s="1">
+        <v>1689.48</v>
+      </c>
+      <c r="F161" s="1">
+        <v>1815.08</v>
+      </c>
+      <c r="G161" s="1">
+        <v>0</v>
+      </c>
+      <c r="H161" s="1">
+        <v>6</v>
+      </c>
+      <c r="I161" s="1">
+        <v>0</v>
+      </c>
+      <c r="J161" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>

--- a/Historical Stats - Money League.xlsx
+++ b/Historical Stats - Money League.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Owner\Documents\Fantasy Sports\Erik Money League\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA5638E9-CEFC-494A-94B5-6DA784F5C448}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F4F572C-DEDF-4C77-9236-1A48DE7A4C56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9276" yWindow="0" windowWidth="13860" windowHeight="12336" xr2:uid="{00571521-F8B7-4EE5-BF3F-816C35BB5F68}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00571521-F8B7-4EE5-BF3F-816C35BB5F68}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="37">
   <si>
     <t>Year</t>
   </si>
@@ -490,7 +490,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91C732AA-F07A-4951-BC9E-EBED592A7799}">
-  <dimension ref="A1:J161"/>
+  <dimension ref="A1:J173"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="7" width="13.77734375" style="1" customWidth="1"/>
@@ -5221,7 +5221,7 @@
         <v>2023</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="C144" s="1">
         <v>7</v>
@@ -5551,7 +5551,7 @@
         <v>2024</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="C154" s="1">
         <v>5</v>
@@ -5807,6 +5807,390 @@
       </c>
       <c r="J161" s="1">
         <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A162" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B162" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C162" s="1">
+        <v>1</v>
+      </c>
+      <c r="D162" s="1">
+        <v>11</v>
+      </c>
+      <c r="E162" s="1">
+        <v>2128.2399999999998</v>
+      </c>
+      <c r="F162" s="1">
+        <v>1886.16</v>
+      </c>
+      <c r="G162" s="1">
+        <v>1</v>
+      </c>
+      <c r="H162" s="1">
+        <v>8</v>
+      </c>
+      <c r="I162" s="1">
+        <v>1</v>
+      </c>
+      <c r="J162" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="163" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A163" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B163" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C163" s="1">
+        <v>2</v>
+      </c>
+      <c r="D163" s="1">
+        <v>8</v>
+      </c>
+      <c r="E163" s="1">
+        <v>1788.14</v>
+      </c>
+      <c r="F163" s="1">
+        <v>1776.9</v>
+      </c>
+      <c r="G163" s="1">
+        <v>1</v>
+      </c>
+      <c r="H163" s="1">
+        <v>6</v>
+      </c>
+      <c r="I163" s="1">
+        <v>0</v>
+      </c>
+      <c r="J163" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A164" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B164" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C164" s="1">
+        <v>3</v>
+      </c>
+      <c r="D164" s="1">
+        <v>7</v>
+      </c>
+      <c r="E164" s="1">
+        <v>1904.84</v>
+      </c>
+      <c r="F164" s="1">
+        <v>1812.26</v>
+      </c>
+      <c r="G164" s="1">
+        <v>1</v>
+      </c>
+      <c r="H164" s="1">
+        <v>9</v>
+      </c>
+      <c r="I164" s="1">
+        <v>0</v>
+      </c>
+      <c r="J164" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A165" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B165" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C165" s="1">
+        <v>4</v>
+      </c>
+      <c r="D165" s="1">
+        <v>9</v>
+      </c>
+      <c r="E165" s="1">
+        <v>1976.58</v>
+      </c>
+      <c r="F165" s="1">
+        <v>1786.6</v>
+      </c>
+      <c r="G165" s="1">
+        <v>1</v>
+      </c>
+      <c r="H165" s="1">
+        <v>3</v>
+      </c>
+      <c r="I165" s="1">
+        <v>1</v>
+      </c>
+      <c r="J165" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A166" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B166" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C166" s="1">
+        <v>5</v>
+      </c>
+      <c r="D166" s="1">
+        <v>8</v>
+      </c>
+      <c r="E166" s="1">
+        <v>1837.5</v>
+      </c>
+      <c r="F166" s="1">
+        <v>1836.44</v>
+      </c>
+      <c r="G166" s="1">
+        <v>1</v>
+      </c>
+      <c r="H166" s="1">
+        <v>1</v>
+      </c>
+      <c r="I166" s="1">
+        <v>0</v>
+      </c>
+      <c r="J166" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A167" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B167" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C167" s="1">
+        <v>6</v>
+      </c>
+      <c r="D167" s="1">
+        <v>8</v>
+      </c>
+      <c r="E167" s="1">
+        <v>1771.08</v>
+      </c>
+      <c r="F167" s="1">
+        <v>1756.18</v>
+      </c>
+      <c r="G167" s="1">
+        <v>1</v>
+      </c>
+      <c r="H167" s="1">
+        <v>2</v>
+      </c>
+      <c r="I167" s="1">
+        <v>0</v>
+      </c>
+      <c r="J167" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A168" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B168" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C168" s="1">
+        <v>7</v>
+      </c>
+      <c r="D168" s="1">
+        <v>6</v>
+      </c>
+      <c r="E168" s="1">
+        <v>1773.88</v>
+      </c>
+      <c r="F168" s="1">
+        <v>1773.92</v>
+      </c>
+      <c r="G168" s="1">
+        <v>0</v>
+      </c>
+      <c r="H168" s="1">
+        <v>12</v>
+      </c>
+      <c r="I168" s="1">
+        <v>0</v>
+      </c>
+      <c r="J168" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A169" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B169" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C169" s="1">
+        <v>8</v>
+      </c>
+      <c r="D169" s="1">
+        <v>7</v>
+      </c>
+      <c r="E169" s="1">
+        <v>1704.54</v>
+      </c>
+      <c r="F169" s="1">
+        <v>1753.98</v>
+      </c>
+      <c r="G169" s="1">
+        <v>0</v>
+      </c>
+      <c r="H169" s="1">
+        <v>11</v>
+      </c>
+      <c r="I169" s="1">
+        <v>0</v>
+      </c>
+      <c r="J169" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A170" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B170" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C170" s="1">
+        <v>9</v>
+      </c>
+      <c r="D170" s="1">
+        <v>6</v>
+      </c>
+      <c r="E170" s="1">
+        <v>1804.32</v>
+      </c>
+      <c r="F170" s="1">
+        <v>1826.44</v>
+      </c>
+      <c r="G170" s="1">
+        <v>0</v>
+      </c>
+      <c r="H170" s="1">
+        <v>7</v>
+      </c>
+      <c r="I170" s="1">
+        <v>0</v>
+      </c>
+      <c r="J170" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A171" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B171" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C171" s="1">
+        <v>10</v>
+      </c>
+      <c r="D171" s="1">
+        <v>6</v>
+      </c>
+      <c r="E171" s="1">
+        <v>1759.64</v>
+      </c>
+      <c r="F171" s="1">
+        <v>1843.58</v>
+      </c>
+      <c r="G171" s="1">
+        <v>0</v>
+      </c>
+      <c r="H171" s="1">
+        <v>5</v>
+      </c>
+      <c r="I171" s="1">
+        <v>0</v>
+      </c>
+      <c r="J171" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A172" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B172" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C172" s="1">
+        <v>11</v>
+      </c>
+      <c r="D172" s="1">
+        <v>4</v>
+      </c>
+      <c r="E172" s="1">
+        <v>1732.7</v>
+      </c>
+      <c r="F172" s="1">
+        <v>1965.34</v>
+      </c>
+      <c r="G172" s="1">
+        <v>0</v>
+      </c>
+      <c r="H172" s="1">
+        <v>10</v>
+      </c>
+      <c r="I172" s="1">
+        <v>0</v>
+      </c>
+      <c r="J172" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A173" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B173" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C173" s="1">
+        <v>12</v>
+      </c>
+      <c r="D173" s="1">
+        <v>4</v>
+      </c>
+      <c r="E173" s="1">
+        <v>1664.24</v>
+      </c>
+      <c r="F173" s="1">
+        <v>1827.9</v>
+      </c>
+      <c r="G173" s="1">
+        <v>0</v>
+      </c>
+      <c r="H173" s="1">
+        <v>4</v>
+      </c>
+      <c r="I173" s="1">
+        <v>0</v>
+      </c>
+      <c r="J173" s="1">
         <v>0</v>
       </c>
     </row>
